--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2707-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2707-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{316D8F27-5E3C-42B5-A5AB-882A37EC3FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{369B94A9-724D-4D03-AABC-045AB641FE47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{1191BD26-7C1F-4970-B1BF-D88F087C8843}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{9065EFE7-93F2-499A-9F3C-AC07F8EEA35D}"/>
   </bookViews>
   <sheets>
     <sheet name="2707-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1643,28 +1643,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{437D003D-046C-41BF-8773-4A6326F5B6F5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4364A6D-4FF0-4A0E-880F-41D3A8F23561}">
   <dimension ref="A1:X81"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1698,7 +1698,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1734,7 +1734,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1854,7 +1854,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2025</v>
       </c>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -2074,7 +2074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>29</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="41">
         <v>2024</v>
       </c>
@@ -2294,7 +2294,7 @@
         <v>7.98</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2368,7 +2368,7 @@
         <v>7.98</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>29</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>29</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2590,7 +2590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2664,7 +2664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2023</v>
       </c>
@@ -2736,7 +2736,7 @@
         <v>6.02</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>6.02</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2884,7 +2884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2958,7 +2958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -3032,7 +3032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -3106,7 +3106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="41">
         <v>2022</v>
       </c>
@@ -3178,7 +3178,7 @@
         <v>4.79</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>29</v>
       </c>
@@ -3252,7 +3252,7 @@
         <v>4.79</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>29</v>
       </c>
@@ -3326,7 +3326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>29</v>
       </c>
@@ -3400,7 +3400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>29</v>
       </c>
@@ -3474,7 +3474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>29</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="39">
         <v>2021</v>
       </c>
@@ -3620,7 +3620,7 @@
         <v>8.67</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>29</v>
       </c>
@@ -3694,7 +3694,7 @@
         <v>8.67</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>29</v>
       </c>
@@ -3768,7 +3768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>29</v>
       </c>
@@ -3842,7 +3842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
         <v>29</v>
       </c>
@@ -3916,7 +3916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
         <v>29</v>
       </c>
@@ -3990,7 +3990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
         <v>29</v>
       </c>
@@ -4064,7 +4064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="41">
         <v>2020</v>
       </c>
@@ -4136,7 +4136,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="16" t="s">
         <v>29</v>
       </c>
@@ -4210,7 +4210,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="16" t="s">
         <v>29</v>
       </c>
@@ -4284,7 +4284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="16" t="s">
         <v>29</v>
       </c>
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="16" t="s">
         <v>29</v>
       </c>
@@ -4432,7 +4432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="16" t="s">
         <v>29</v>
       </c>
@@ -4506,7 +4506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="16" t="s">
         <v>29</v>
       </c>
@@ -4580,7 +4580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="39">
         <v>2019</v>
       </c>
@@ -4652,7 +4652,7 @@
         <v>8.94</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
         <v>29</v>
       </c>
@@ -4726,7 +4726,7 @@
         <v>4.3600000000000003</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
         <v>29</v>
       </c>
@@ -4800,7 +4800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="11" t="s">
         <v>29</v>
       </c>
@@ -4874,7 +4874,7 @@
         <v>4.59</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="41">
         <v>2018</v>
       </c>
@@ -4946,7 +4946,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="39">
         <v>2017</v>
       </c>
@@ -5018,7 +5018,7 @@
         <v>5.32</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="41">
         <v>2016</v>
       </c>
@@ -5090,7 +5090,7 @@
         <v>5.44</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="39">
         <v>2015</v>
       </c>
@@ -5162,7 +5162,7 @@
         <v>5.28</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="43">
         <v>2014</v>
       </c>
@@ -5234,7 +5234,7 @@
         <v>5.67</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="45"/>
       <c r="B51" s="46"/>
       <c r="C51" s="20" t="s">
@@ -5262,7 +5262,7 @@
       <c r="W51" s="54"/>
       <c r="X51" s="48"/>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="55">
         <v>2013</v>
       </c>
@@ -5334,7 +5334,7 @@
         <v>3.09</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="57"/>
       <c r="B53" s="58"/>
       <c r="C53" s="22" t="s">
@@ -5362,7 +5362,7 @@
       <c r="W53" s="64"/>
       <c r="X53" s="60"/>
     </row>
-    <row r="54" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="43">
         <v>2012</v>
       </c>
@@ -5434,7 +5434,7 @@
         <v>3.17</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="45"/>
       <c r="B55" s="46"/>
       <c r="C55" s="20" t="s">
@@ -5462,7 +5462,7 @@
       <c r="W55" s="54"/>
       <c r="X55" s="48"/>
     </row>
-    <row r="56" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="55">
         <v>2011</v>
       </c>
@@ -5534,7 +5534,7 @@
         <v>4.3899999999999997</v>
       </c>
     </row>
-    <row r="57" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="57"/>
       <c r="B57" s="58"/>
       <c r="C57" s="22" t="s">
@@ -5562,7 +5562,7 @@
       <c r="W57" s="64"/>
       <c r="X57" s="60"/>
     </row>
-    <row r="58" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="43">
         <v>2010</v>
       </c>
@@ -5634,7 +5634,7 @@
         <v>2.96</v>
       </c>
     </row>
-    <row r="59" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="45"/>
       <c r="B59" s="46"/>
       <c r="C59" s="20" t="s">
@@ -5662,7 +5662,7 @@
       <c r="W59" s="54"/>
       <c r="X59" s="48"/>
     </row>
-    <row r="60" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A60" s="55">
         <v>2009</v>
       </c>
@@ -5734,7 +5734,7 @@
         <v>3.01</v>
       </c>
     </row>
-    <row r="61" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A61" s="57"/>
       <c r="B61" s="58"/>
       <c r="C61" s="22" t="s">
@@ -5762,7 +5762,7 @@
       <c r="W61" s="64"/>
       <c r="X61" s="60"/>
     </row>
-    <row r="62" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A62" s="43">
         <v>2008</v>
       </c>
@@ -5834,7 +5834,7 @@
         <v>4.6399999999999997</v>
       </c>
     </row>
-    <row r="63" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A63" s="45"/>
       <c r="B63" s="46"/>
       <c r="C63" s="20" t="s">
@@ -5862,7 +5862,7 @@
       <c r="W63" s="54"/>
       <c r="X63" s="48"/>
     </row>
-    <row r="64" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A64" s="55">
         <v>2007</v>
       </c>
@@ -5934,7 +5934,7 @@
         <v>9.4700000000000006</v>
       </c>
     </row>
-    <row r="65" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A65" s="57"/>
       <c r="B65" s="58"/>
       <c r="C65" s="22" t="s">
@@ -5962,7 +5962,7 @@
       <c r="W65" s="64"/>
       <c r="X65" s="60"/>
     </row>
-    <row r="66" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A66" s="41">
         <v>2006</v>
       </c>
@@ -6034,7 +6034,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="67" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A67" s="39">
         <v>2005</v>
       </c>
@@ -6106,7 +6106,7 @@
         <v>6.34</v>
       </c>
     </row>
-    <row r="68" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A68" s="41">
         <v>2004</v>
       </c>
@@ -6178,7 +6178,7 @@
         <v>7.35</v>
       </c>
     </row>
-    <row r="69" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A69" s="39">
         <v>2003</v>
       </c>
@@ -6250,7 +6250,7 @@
         <v>7.28</v>
       </c>
     </row>
-    <row r="70" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A70" s="41">
         <v>2002</v>
       </c>
@@ -6322,7 +6322,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="71" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A71" s="39">
         <v>2001</v>
       </c>
@@ -6394,7 +6394,7 @@
         <v>6.71</v>
       </c>
     </row>
-    <row r="72" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A72" s="41">
         <v>2000</v>
       </c>
@@ -6466,7 +6466,7 @@
         <v>9.3800000000000008</v>
       </c>
     </row>
-    <row r="73" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A73" s="39">
         <v>1999</v>
       </c>
@@ -6538,7 +6538,7 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="74" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A74" s="41">
         <v>1998</v>
       </c>
@@ -6610,7 +6610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A75" s="39">
         <v>1997</v>
       </c>
@@ -6682,7 +6682,7 @@
         <v>9.74</v>
       </c>
     </row>
-    <row r="76" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A76" s="41">
         <v>1996</v>
       </c>
@@ -6754,7 +6754,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="77" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A77" s="39">
         <v>1995</v>
       </c>
@@ -6826,7 +6826,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="78" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A78" s="41">
         <v>1994</v>
       </c>
@@ -6898,7 +6898,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="79" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A79" s="39">
         <v>1993</v>
       </c>
@@ -6970,7 +6970,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="80" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A80" s="41">
         <v>1992</v>
       </c>
@@ -7042,7 +7042,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="81" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A81" s="39" t="s">
         <v>76</v>
       </c>
